--- a/artfynd/A 2839-2026 artfynd.xlsx
+++ b/artfynd/A 2839-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,228 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132660171</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58108</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Aggarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>403749</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6211295</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132660199</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57962</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aggarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>403749</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6211295</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2839-2026 artfynd.xlsx
+++ b/artfynd/A 2839-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>132660171</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>132660199</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2839-2026 artfynd.xlsx
+++ b/artfynd/A 2839-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>132660171</v>
       </c>
       <c r="B3" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>132660199</v>
       </c>
       <c r="B4" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2839-2026 artfynd.xlsx
+++ b/artfynd/A 2839-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660199</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130955886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,8 +1137,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132660171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>